--- a/data-manipulation-scripts/sheets-cleanup/sheets/PARALAMA NOVO 18_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/PARALAMA NOVO 18_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>PARALAMA DIANTEIRO WESTER PRETO INJETADO TITAN125 2000 A 2004/ FAN125 2005 A 2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -437,7 +440,9 @@
       <c r="D9" s="4"/>
     </row>
     <row r="10">
-      <c r="A10" s="3"/>
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
